--- a/New_CenterOfRotation/Finite_COR/Data Files/C45_Data/Model 14 Y_Z Data.xlsx
+++ b/New_CenterOfRotation/Finite_COR/Data Files/C45_Data/Model 14 Y_Z Data.xlsx
@@ -4,7 +4,7 @@
   <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="0"/>
+    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet r:id="rId1" sheetId="1" name="4N"/>
@@ -75,9 +75,6 @@
     <t>Middle Back Top of C5</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
     <t>Node</t>
   </si>
   <si>
@@ -88,6 +85,9 @@
   </si>
   <si>
     <t>X (U1)</t>
+  </si>
+  <si>
+    <t/>
   </si>
 </sst>
 </file>
@@ -233,9 +233,6 @@
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="3" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="3" applyFont="1" fillId="3" applyFill="1" quotePrefix="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="3" applyFont="1" fillId="3" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -255,6 +252,9 @@
       <alignment horizontal="right"/>
     </xf>
     <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="3" applyFont="1" fillId="3" applyFill="1" quotePrefix="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="1" applyFont="1" fillId="3" applyFill="1" quotePrefix="1" applyAlignment="1">
@@ -3727,8 +3727,8 @@
       <c r="AC2" s="16"/>
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
-      <c r="A3" s="18" t="s">
-        <v>18</v>
+      <c r="A3" s="25" t="s">
+        <v>22</v>
       </c>
       <c r="B3" s="6">
         <v>25454</v>
@@ -3736,8 +3736,8 @@
       <c r="C3" s="5"/>
       <c r="D3" s="5"/>
       <c r="E3" s="3"/>
-      <c r="F3" s="18" t="s">
-        <v>18</v>
+      <c r="F3" s="25" t="s">
+        <v>22</v>
       </c>
       <c r="G3" s="6">
         <v>31067</v>
@@ -3745,8 +3745,8 @@
       <c r="H3" s="5"/>
       <c r="I3" s="5"/>
       <c r="J3" s="3"/>
-      <c r="K3" s="18" t="s">
-        <v>18</v>
+      <c r="K3" s="25" t="s">
+        <v>22</v>
       </c>
       <c r="L3" s="1">
         <v>29005</v>
@@ -3754,8 +3754,8 @@
       <c r="M3" s="2"/>
       <c r="N3" s="2"/>
       <c r="O3" s="3"/>
-      <c r="P3" s="18" t="s">
-        <v>18</v>
+      <c r="P3" s="25" t="s">
+        <v>22</v>
       </c>
       <c r="Q3" s="1">
         <v>45615</v>
@@ -3763,8 +3763,8 @@
       <c r="R3" s="2"/>
       <c r="S3" s="2"/>
       <c r="T3" s="3"/>
-      <c r="U3" s="18" t="s">
-        <v>18</v>
+      <c r="U3" s="25" t="s">
+        <v>22</v>
       </c>
       <c r="V3" s="1">
         <v>52027</v>
@@ -3773,90 +3773,90 @@
       <c r="X3" s="2"/>
       <c r="Y3" s="3"/>
       <c r="Z3" s="26" t="s">
-        <v>18</v>
-      </c>
-      <c r="AA3" s="21">
+        <v>22</v>
+      </c>
+      <c r="AA3" s="20">
         <v>49903</v>
       </c>
       <c r="AB3" s="2"/>
       <c r="AC3" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="19.5">
-      <c r="A4" s="22" t="s">
-        <v>21</v>
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
+      <c r="A4" s="21" t="s">
+        <v>20</v>
       </c>
       <c r="B4" s="7">
         <v>-6.65384</v>
       </c>
-      <c r="C4" s="23">
+      <c r="C4" s="22">
         <v>441.175</v>
       </c>
       <c r="D4" s="7">
         <v>-709.18</v>
       </c>
       <c r="E4" s="3"/>
-      <c r="F4" s="22" t="s">
-        <v>21</v>
+      <c r="F4" s="21" t="s">
+        <v>20</v>
       </c>
       <c r="G4" s="7">
         <v>6.11839</v>
       </c>
-      <c r="H4" s="24">
+      <c r="H4" s="23">
         <v>439.835</v>
       </c>
       <c r="I4" s="7">
         <v>-709.539</v>
       </c>
       <c r="J4" s="3"/>
-      <c r="K4" s="22" t="s">
-        <v>21</v>
+      <c r="K4" s="21" t="s">
+        <v>20</v>
       </c>
       <c r="L4" s="2">
         <v>0.185553</v>
       </c>
-      <c r="M4" s="24">
+      <c r="M4" s="23">
         <v>446.547</v>
       </c>
       <c r="N4" s="2">
         <v>-707.74</v>
       </c>
       <c r="O4" s="3"/>
-      <c r="P4" s="22" t="s">
-        <v>21</v>
+      <c r="P4" s="21" t="s">
+        <v>20</v>
       </c>
       <c r="Q4" s="2">
         <v>-8.27627</v>
       </c>
-      <c r="R4" s="23">
+      <c r="R4" s="22">
         <v>440.046</v>
       </c>
       <c r="S4" s="2">
         <v>-714.179</v>
       </c>
       <c r="T4" s="3"/>
-      <c r="U4" s="22" t="s">
-        <v>21</v>
+      <c r="U4" s="21" t="s">
+        <v>20</v>
       </c>
       <c r="V4" s="2">
         <v>7.72579</v>
       </c>
-      <c r="W4" s="24">
+      <c r="W4" s="23">
         <v>440.224</v>
       </c>
       <c r="X4" s="2">
         <v>-714.622</v>
       </c>
       <c r="Y4" s="3"/>
-      <c r="Z4" s="22" t="s">
-        <v>21</v>
-      </c>
-      <c r="AA4" s="24">
+      <c r="Z4" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="AA4" s="23">
         <v>-0.0172085</v>
       </c>
-      <c r="AB4" s="23">
+      <c r="AB4" s="22">
         <v>445.307</v>
       </c>
-      <c r="AC4" s="24">
+      <c r="AC4" s="23">
         <v>-714.355</v>
       </c>
     </row>
@@ -3864,8 +3864,8 @@
       <c r="A5" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="25" t="s">
-        <v>22</v>
+      <c r="B5" s="24" t="s">
+        <v>21</v>
       </c>
       <c r="C5" s="5" t="s">
         <v>7</v>
@@ -3877,8 +3877,8 @@
       <c r="F5" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="G5" s="25" t="s">
-        <v>22</v>
+      <c r="G5" s="24" t="s">
+        <v>21</v>
       </c>
       <c r="H5" s="5" t="s">
         <v>7</v>
@@ -3890,8 +3890,8 @@
       <c r="K5" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="L5" s="25" t="s">
-        <v>22</v>
+      <c r="L5" s="24" t="s">
+        <v>21</v>
       </c>
       <c r="M5" s="5" t="s">
         <v>7</v>
@@ -3903,8 +3903,8 @@
       <c r="P5" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="Q5" s="25" t="s">
-        <v>22</v>
+      <c r="Q5" s="24" t="s">
+        <v>21</v>
       </c>
       <c r="R5" s="5" t="s">
         <v>7</v>
@@ -3916,8 +3916,8 @@
       <c r="U5" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="V5" s="25" t="s">
-        <v>22</v>
+      <c r="V5" s="24" t="s">
+        <v>21</v>
       </c>
       <c r="W5" s="5" t="s">
         <v>7</v>
@@ -3929,8 +3929,8 @@
       <c r="Z5" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AA5" s="25" t="s">
-        <v>22</v>
+      <c r="AA5" s="24" t="s">
+        <v>21</v>
       </c>
       <c r="AB5" s="5" t="s">
         <v>7</v>
@@ -5883,8 +5883,8 @@
       <c r="R3" s="2"/>
       <c r="S3" s="2"/>
       <c r="T3" s="3"/>
-      <c r="U3" s="19" t="s">
-        <v>19</v>
+      <c r="U3" s="18" t="s">
+        <v>18</v>
       </c>
       <c r="V3" s="1">
         <v>52027</v>
@@ -5892,91 +5892,91 @@
       <c r="W3" s="2"/>
       <c r="X3" s="2"/>
       <c r="Y3" s="3"/>
-      <c r="Z3" s="20" t="s">
-        <v>20</v>
-      </c>
-      <c r="AA3" s="21">
+      <c r="Z3" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="AA3" s="20">
         <v>49903</v>
       </c>
       <c r="AB3" s="2"/>
       <c r="AC3" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
-      <c r="A4" s="22" t="s">
-        <v>21</v>
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="19.5">
+      <c r="A4" s="21" t="s">
+        <v>20</v>
       </c>
       <c r="B4" s="7">
         <v>-6.65384</v>
       </c>
-      <c r="C4" s="23">
+      <c r="C4" s="22">
         <v>441.175</v>
       </c>
       <c r="D4" s="7">
         <v>-709.18</v>
       </c>
       <c r="E4" s="3"/>
-      <c r="F4" s="22" t="s">
-        <v>21</v>
+      <c r="F4" s="21" t="s">
+        <v>20</v>
       </c>
       <c r="G4" s="7">
         <v>6.11839</v>
       </c>
-      <c r="H4" s="24">
+      <c r="H4" s="23">
         <v>439.835</v>
       </c>
       <c r="I4" s="7">
         <v>-709.539</v>
       </c>
       <c r="J4" s="3"/>
-      <c r="K4" s="22" t="s">
-        <v>21</v>
+      <c r="K4" s="21" t="s">
+        <v>20</v>
       </c>
       <c r="L4" s="2">
         <v>0.185553</v>
       </c>
-      <c r="M4" s="24">
+      <c r="M4" s="23">
         <v>446.547</v>
       </c>
       <c r="N4" s="2">
         <v>-707.74</v>
       </c>
       <c r="O4" s="3"/>
-      <c r="P4" s="22" t="s">
-        <v>21</v>
+      <c r="P4" s="21" t="s">
+        <v>20</v>
       </c>
       <c r="Q4" s="2">
         <v>-8.27627</v>
       </c>
-      <c r="R4" s="23">
+      <c r="R4" s="22">
         <v>440.046</v>
       </c>
       <c r="S4" s="2">
         <v>-714.179</v>
       </c>
       <c r="T4" s="3"/>
-      <c r="U4" s="22" t="s">
-        <v>21</v>
+      <c r="U4" s="21" t="s">
+        <v>20</v>
       </c>
       <c r="V4" s="2">
         <v>7.72579</v>
       </c>
-      <c r="W4" s="24">
+      <c r="W4" s="23">
         <v>440.224</v>
       </c>
       <c r="X4" s="2">
         <v>-714.622</v>
       </c>
       <c r="Y4" s="3"/>
-      <c r="Z4" s="22" t="s">
-        <v>21</v>
-      </c>
-      <c r="AA4" s="24">
+      <c r="Z4" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="AA4" s="23">
         <v>-0.0172085</v>
       </c>
-      <c r="AB4" s="23">
+      <c r="AB4" s="22">
         <v>445.307</v>
       </c>
-      <c r="AC4" s="24">
+      <c r="AC4" s="23">
         <v>-714.355</v>
       </c>
     </row>
@@ -5984,8 +5984,8 @@
       <c r="A5" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="25" t="s">
-        <v>22</v>
+      <c r="B5" s="24" t="s">
+        <v>21</v>
       </c>
       <c r="C5" s="5" t="s">
         <v>7</v>
@@ -5997,8 +5997,8 @@
       <c r="F5" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="G5" s="25" t="s">
-        <v>22</v>
+      <c r="G5" s="24" t="s">
+        <v>21</v>
       </c>
       <c r="H5" s="5" t="s">
         <v>7</v>
@@ -6010,8 +6010,8 @@
       <c r="K5" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="L5" s="25" t="s">
-        <v>22</v>
+      <c r="L5" s="24" t="s">
+        <v>21</v>
       </c>
       <c r="M5" s="5" t="s">
         <v>7</v>
@@ -6023,8 +6023,8 @@
       <c r="P5" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="Q5" s="25" t="s">
-        <v>22</v>
+      <c r="Q5" s="24" t="s">
+        <v>21</v>
       </c>
       <c r="R5" s="5" t="s">
         <v>7</v>
@@ -6036,8 +6036,8 @@
       <c r="U5" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="V5" s="25" t="s">
-        <v>22</v>
+      <c r="V5" s="24" t="s">
+        <v>21</v>
       </c>
       <c r="W5" s="5" t="s">
         <v>7</v>
@@ -6049,8 +6049,8 @@
       <c r="Z5" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="AA5" s="25" t="s">
-        <v>22</v>
+      <c r="AA5" s="24" t="s">
+        <v>21</v>
       </c>
       <c r="AB5" s="5" t="s">
         <v>7</v>
